--- a/data/31August-Towers-v-Razorbacks.xlsx
+++ b/data/31August-Towers-v-Razorbacks.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="R5c59be49e2944bfd"/>
@@ -153,9 +153,39 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" mc:Ignorable="x14ac">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);(&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);(&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red](&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* (#,##0.00);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* (#,##0.00);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+  </fonts>
+  <fills count="1">
+    <fill/>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O120"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -170,7 +200,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">

--- a/data/31August-Towers-v-Razorbacks.xlsx
+++ b/data/31August-Towers-v-Razorbacks.xlsx
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac">
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -465,8 +465,10 @@
       <c r="D27" t="s">
         <v>19</v>
       </c>
-      <c r="E27" t="s">
-        <v>22</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LCDC</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -643,8 +645,10 @@
       <c r="D47" t="s">
         <v>19</v>
       </c>
-      <c r="E47" t="s">
-        <v>25</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -724,8 +728,10 @@
       <c r="D56" t="s">
         <v>19</v>
       </c>
-      <c r="E56" t="s">
-        <v>25</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="57">
